--- a/output/pdf_financials_xlsx/DCNN.X.xlsx
+++ b/output/pdf_financials_xlsx/DCNN.X.xlsx
@@ -431,6 +431,13 @@
   </sheetPr>
   <dimension ref="A1:E135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/DCNN.X.xlsx
+++ b/output/pdf_financials_xlsx/DCNN.X.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.00018</v>
+        <v>0.00018</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-5.322011</v>
+        <v>5.322011</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>-3.571655</v>
+        <v>3.571655</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>-0.895151</v>
+        <v>0.895151</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0.134855</v>
@@ -670,16 +670,16 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -2351,25 +2351,17 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-41.934737</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>17.771282</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-0.576264</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>-0.428538</v>
       </c>
     </row>
     <row r="100">
@@ -2378,25 +2370,17 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2405,25 +2389,17 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0.526787</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0.09867099999999999</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0.006837</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2432,25 +2408,17 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0.002985</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0.077891</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2459,25 +2427,17 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0.02535</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0.000121</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>-0.004583</v>
       </c>
     </row>
     <row r="104">
@@ -2486,25 +2446,17 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>-0.301073</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>-2.582458</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>0.150689</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>0.252659</v>
       </c>
     </row>
     <row r="105">
@@ -2513,25 +2465,17 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2540,25 +2484,17 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.254049</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>-2.405775</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>0.157526</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>0.248076</v>
       </c>
     </row>
     <row r="107">
@@ -2567,25 +2503,17 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0.088852</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0.041096</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0.033937</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -2594,25 +2522,17 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2621,25 +2541,17 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2648,25 +2560,17 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2675,25 +2579,17 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2702,25 +2598,17 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2729,25 +2617,17 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2756,25 +2636,17 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2783,25 +2655,17 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2810,25 +2674,17 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2837,25 +2693,17 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2864,25 +2712,17 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2891,20 +2731,14 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>-1.263498</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>3.182258</v>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>-0.006837</v>
       </c>
       <c r="E119" s="1" t="inlineStr">
         <is>
@@ -2918,25 +2752,17 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2945,25 +2771,17 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2972,25 +2790,17 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2999,25 +2809,17 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3026,25 +2828,17 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3053,25 +2847,17 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3080,25 +2866,17 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3134,25 +2912,17 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3171,10 +2941,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D129" s="3" t="n">
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E129" s="1" t="inlineStr">
         <is>
@@ -3188,25 +2956,17 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>3.093357</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>0.304255</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>0.738742</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>0.293907</v>
       </c>
     </row>
     <row r="131">
@@ -3215,25 +2975,17 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3242,25 +2994,17 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-2.754093</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>0.434487</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>-0.444835</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>-0.110835</v>
       </c>
     </row>
     <row r="133">
@@ -3269,25 +3013,17 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.304255</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>0.738742</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>0.293907</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>0.183072</v>
       </c>
     </row>
     <row r="134">
@@ -3296,25 +3032,17 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3333,15 +3061,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D135" s="3" t="n">
+        <v>-0.367998</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>-0.185835</v>
       </c>
     </row>
   </sheetData>
@@ -3355,7 +3079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H170"/>
+  <dimension ref="A1:H239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4749,7 +4473,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities 14,19 $</t>
+          <t>Accounts payable and accrued liabilities 14, 19 $</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5071,16 +4795,24 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>OPERATING ACTIVITIES</t>
+        </is>
+      </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>December 31, 2025 December</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -5092,26 +4824,26 @@
         </is>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.002024</v>
+        <v>-0.576264</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>-0.428538</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Consulting and management 10</t>
+          <t>Finance and other costs 6</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -5126,56 +4858,60 @@
         </is>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.33424</v>
+        <v>0.254921</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>0.30059</v>
+        <v>0.263551</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Corporate development</t>
+          <t>Gain on debt settlement 7, 9</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" s="5" t="n">
-        <v>0.042849</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>0.03792</v>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.010683</v>
+        <v>-0.075054</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>0.004811</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Finance and other costs 7</t>
+          <t>Gain on modification of debt 7</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -5190,60 +4926,62 @@
         </is>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.254921</v>
+        <v>-0.163514</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>0.263551</v>
+        <v>-0.163924</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="n">
-        <v>0.051064</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>0.126367</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>0.018205</v>
+          <t>Gain on loan forgiveness 8</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H51" s="5" t="n">
-        <v>0.057312</v>
+        <v>-0.075</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Investor communication</t>
+          <t>Unrealized loss on marketable securities</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -5252,131 +4990,153 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F52" s="5" t="n">
-        <v>0.000514</v>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.00363</v>
-      </c>
-      <c r="H52" s="5" t="n">
-        <v>0.003894</v>
+        <v>0.00045</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Office and sundry</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" s="5" t="n">
-        <v>0.028025</v>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>0.06821000000000001</v>
+          <t>Share-based payments 9</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.009617000000000001</v>
-      </c>
-      <c r="H53" s="5" t="n">
-        <v>0.002882</v>
+        <v>0.033937</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Derecognition of accounts payable</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>0.635392</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>0.382852</v>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.165034</v>
+        <v>-0.073932</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>0.08397499999999999</v>
+        <v>-0.000599</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Regulatory and transfer agent fees</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>0.176834</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>0.152018</v>
+          <t>Adjustments for total</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.07457</v>
+        <v>-0.599456</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>0.077543</v>
+        <v>-0.43451</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Share-based payments</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>Amounts receivable</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -5388,7 +5148,7 @@
         </is>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.033937</v>
+        <v>0.006837</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -5399,20 +5159,24 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Wages and salaries (recoveries)</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>Prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -5423,64 +5187,74 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G57" s="5" t="n">
-        <v>-0.009686</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H57" s="5" t="n">
-        <v>0.003503</v>
+        <v>-0.004583</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Loss before other items</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="n">
-        <v>-5.321992</v>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>-3.571655</v>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.895151</v>
+        <v>0.224621</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>-0.798061</v>
+        <v>0.253258</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Gain on debt settlement 7, 9</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>Cash flows used in operating activities</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -5492,26 +5266,26 @@
         </is>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.075054</v>
+        <v>-0.367998</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>0.03</v>
+        <v>-0.185835</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Gain on loan forgiveness 8</t>
+          <t>Gain for the period from discontinued operations 14</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -5525,29 +5299,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="5" t="n">
-        <v>0.075</v>
+      <c r="G60" s="5" t="n">
+        <v>-0.006837</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Net cash used in operating activities from continued</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Gain on modification of debt 7</t>
+          <t>Net cash used in operating activities from continued total</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -5562,26 +5336,26 @@
         </is>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.163514</v>
+        <v>-0.374835</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>0.163924</v>
+        <v>-0.185835</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Gain on termination of proposed transaction 8</t>
+          <t>Repayment of loans 8</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -5595,29 +5369,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" s="5" t="n">
-        <v>0.1</v>
+      <c r="G62" s="5" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Unrealized loss on marketable securities 4</t>
+          <t>Receipt of loans 8</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -5626,32 +5400,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F63" s="5" t="n">
-        <v>-0.49955</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>-0.00045</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>0.075</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Derecognition of accounts payable 6</t>
+          <t>Cash received from (used in) financing activities</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -5666,29 +5442,33 @@
         </is>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.073932</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>0.000599</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Total other items</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>Decrease in cash</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -5700,29 +5480,33 @@
         </is>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.31205</v>
+        <v>-0.444835</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>0.369523</v>
+        <v>-0.110835</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss for the year for</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss for the year for continuing operations</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>Cash, beginning of the year</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -5734,29 +5518,33 @@
         </is>
       </c>
       <c r="G66" s="5" t="n">
-        <v>-0.583101</v>
+        <v>0.738742</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>-0.428538</v>
+        <v>0.293907</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss for the year for</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Net income for the year for discontinued operations 14</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>Cash, end of the year</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -5768,121 +5556,107 @@
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.006837</v>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.293907</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>0.183072</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss for the year for</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Net income (loss) for the year</t>
+          <t>Net income (loss) for the year $</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>-41.934737</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>17.771282</v>
       </c>
       <c r="G68" s="5" t="n">
         <v>-0.576264</v>
       </c>
-      <c r="H68" s="5" t="n">
-        <v>-0.428538</v>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Net income (loss) attributable to</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Shareholders of Digicann Ventures Inc.</t>
+          <t>Finance and other costs</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E69" s="5" t="n">
+        <v>3.297199</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>2.219767</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>-0.576264</v>
-      </c>
-      <c r="H69" s="5" t="n">
-        <v>-0.428538</v>
+        <v>0.254921</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Net income (loss) attributable to</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Non-controlling interests</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>MinorityInterests</t>
-        </is>
-      </c>
+          <t>Gain on debt settlement 9</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F70" s="5" t="n">
+        <v>-16.157433</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>-0.075054</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -5893,17 +5667,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Net income (loss) attributable to</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Net income (loss) attributable to total</t>
+          <t>Gain on modification of debt 9</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -5913,29 +5687,31 @@
         </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>17.809552</v>
+        <v>-0.643019</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>-0.576264</v>
-      </c>
-      <c r="H71" s="5" t="n">
-        <v>-0.428538</v>
+        <v>-0.163514</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Net and comprehensive income (loss) attributable to</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Shareholders of Digicann Ventures Inc.</t>
+          <t>Gain on loan forgiveness 11</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -5944,48 +5720,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="n">
-        <v>-0.576264</v>
-      </c>
-      <c r="H72" s="5" t="n">
-        <v>-0.428538</v>
+      <c r="F72" s="5" t="n">
+        <v>-0.754383</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Net and comprehensive income (loss) attributable to</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Non-controlling interests</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>MinorityInterests</t>
-        </is>
-      </c>
+          <t>Loss on sale of marketable securities 4</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F73" s="5" t="n">
+        <v>0.081</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -6001,17 +5773,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Net and comprehensive income (loss) attributable to</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Net and comprehensive income (loss) attributable to total</t>
+          <t>Unrealized loss on marketable securities 4</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -6021,29 +5793,31 @@
         </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>17.771282</v>
+        <v>0.49955</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>-0.576264</v>
-      </c>
-      <c r="H74" s="5" t="n">
-        <v>-0.428538</v>
+        <v>0.00045</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Net and comprehensive income (loss) attributable to</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Net income (loss) per share for continuing operations - basic $</t>
+          <t>Shares issued for interest expense 11</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -6052,177 +5826,191 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="H75" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="F75" s="5" t="n">
+        <v>0.059066</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Net income (loss) per share for discontinued operations</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>- basic $</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>Share-based payments 11</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F76" s="5" t="n">
+        <v>0.041096</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="5" t="n">
-        <v>0</v>
+        <v>0.033937</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Net income (loss) per share for discontinued operations</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Net income (loss) per share - basic $</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Deferred revenues recognized 15</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="H77" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="F77" s="5" t="n">
+        <v>-0.297001</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Net income (loss) per share for discontinued operations</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Net income (loss) per share for continuing operations - diluted $</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>Derecognition of accounts payable 8</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F78" s="5" t="n">
+        <v>-0.679417</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="H78" s="5" t="n">
-        <v>-2e-08</v>
+        <v>-0.073932</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Net income (loss) per share for discontinued operations</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>- diluted $</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>Write-off of accounts receivable</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="5" t="n">
-        <v>0</v>
+      <c r="F79" s="5" t="n">
+        <v>0.000125</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Net income (loss) per share for discontinued operations</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Net income (loss) per share - diluted $</t>
+          <t>Write-off of prepaid expenses</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>DilutedEPS</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -6230,155 +6018,157 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="H80" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="F80" s="5" t="n">
+        <v>0.000121</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Net income (loss) per share for discontinued operations</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>W eighted average number of common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="n">
-        <v>21.12015</v>
-      </c>
-      <c r="H81" s="5" t="n">
-        <v>22.844335</v>
+      <c r="F81" s="5" t="n">
+        <v>-0.012461</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2023 17,856,672 204,391,087 4,545,209 7,993,945 (129,897) (6,153)</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts receivable</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>0.301088</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>0.09854599999999999</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>-0.62036</v>
-      </c>
-      <c r="H82" s="5" t="n">
-        <v>-217.414551</v>
+        <v>0.006837</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Fair value of options expired (Note 9) - - (1,906,814) - - -</t>
+          <t>Prepaids and deposits</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E83" s="5" t="n">
+        <v>-0.031215</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>0.056942</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H83" s="5" t="n">
-        <v>1.906814</v>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Share-based payments - Restricted Share Units (Note 9) - - 33,937 - - -</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G84" s="5" t="n">
-        <v>0.033937</v>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ChangeInInventory</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>0.002985</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>0.077891</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -6389,34 +6179,32 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Shares issued for conversion of Restricted Share Units (Note 9) 1,696,815 33,937 (33,937) - - -</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>-0.053673</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>-1.903041</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>0.224621</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -6427,32 +6215,28 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Shares issued for debt settlement (Note 9) 2,501,807 50,036 - - - -</t>
+          <t>Net cash flows received from (used in) operating activities</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E86" s="5" t="n">
+        <v>-23.057874</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>0.458631</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.050036</v>
+        <v>-0.367998</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -6463,55 +6247,51 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year - - - - - -</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Net income for the year from discontinued operations 1, 5, 16</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F87" s="5" t="n">
+        <v>-3.206402</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>-0.576264</v>
-      </c>
-      <c r="H87" s="5" t="n">
-        <v>-0.576264</v>
+        <v>-0.006837</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Net cash used in operating activities from continued</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2024 22,055,294 204,475,060 2,638,395 7,993,945 (129,897) (6,153)</t>
+          <t>Net cash used in operating activities from continued operations</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -6520,32 +6300,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F88" s="5" t="n">
+        <v>-2.747771</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>-1.112651</v>
-      </c>
-      <c r="H88" s="5" t="n">
-        <v>-216.084001</v>
+        <v>-0.374835</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Shares issued for debt settlement (Note 9) 1,000,000 20,000 - - - -</t>
+          <t>Repayment of loans 10</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -6560,7 +6340,7 @@
         </is>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -6571,20 +6351,24 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Fair value of options expired (Note 9) - - (2,616,181) - - -</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
+          <t>Net cash flows used in financing activities</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -6595,29 +6379,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H90" s="5" t="n">
-        <v>2.616181</v>
+      <c r="G90" s="5" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Fair value of warrants expired (Note 9) - - - (7,993,945) - -</t>
+          <t>Sale of AgraFlora Europe 16</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -6626,34 +6410,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F91" s="5" t="n">
+        <v>0.60822</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H91" s="5" t="n">
-        <v>7.993945</v>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2025 23,055,294 204,495,060 22,214 - (129,897) (6,153)</t>
+          <t>Recovery of loan receivable 7</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -6662,45 +6446,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>-1.521189</v>
-      </c>
-      <c r="H92" s="5" t="n">
-        <v>-205.902413</v>
+      <c r="F92" s="5" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Consulting and management 12</t>
+          <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E93" s="5" t="n">
+        <v>0.008312</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>0.491472</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>0.33424</v>
+        <v>2.349038</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -6711,30 +6497,36 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Finance and other costs 9, 10</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>Net cash flows provided by investing activities</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F94" s="5" t="n">
-        <v>2.278833</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>0.254921</v>
+        <v>3.182258</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -6745,36 +6537,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (gain)</t>
+          <t>Change in cash</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>-2.754093</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>-0.012461</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.434487</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>-0.444835</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -6785,30 +6573,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Share-based payments 11</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>3.093357</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>0.041096</v>
+        <v>0.304255</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.033937</v>
+        <v>0.738742</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -6819,30 +6609,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Wages and salary recoveries</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, end of year $</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>0.304255</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>0.004834</v>
+        <v>0.738742</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>-0.009686</v>
+        <v>0.293907</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -6853,32 +6645,36 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Expenses total</t>
+          <t>Amortization (Notes 7 and 8)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>-5.322011</v>
-      </c>
-      <c r="F98" s="5" t="n">
-        <v>-3.571655</v>
-      </c>
-      <c r="G98" s="5" t="n">
-        <v>-0.895151</v>
+        <v>0.145242</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -6889,30 +6685,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Gain on debt settlement 9,11</t>
+          <t>Interest income (Note 5)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F99" s="5" t="n">
-        <v>16.157433</v>
-      </c>
-      <c r="G99" s="5" t="n">
-        <v>0.075054</v>
+      <c r="E99" s="5" t="n">
+        <v>-0.657651</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -6923,27 +6721,27 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Gain on loan forgiveness 10</t>
+          <t>Gain on termination of lease (Note 15)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F100" s="5" t="n">
-        <v>0.754383</v>
+      <c r="E100" s="5" t="n">
+        <v>-0.159614</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -6959,30 +6757,30 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Gain on modification of debt 9</t>
+          <t>Gain on debt settlement (Note 18)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E101" s="5" t="n">
+        <v>-3.381551</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>0.643019</v>
-      </c>
-      <c r="G101" s="5" t="n">
-        <v>0.163514</v>
+        <v>-16.157433</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -6993,30 +6791,30 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Derecognition of accounts payable 8</t>
+          <t>Gain on modification of debt (Note 16)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E102" s="5" t="n">
+        <v>-1.529911</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>0.679417</v>
-      </c>
-      <c r="G102" s="5" t="n">
-        <v>0.073932</v>
+        <v>-0.643019</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -7027,17 +6825,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Gain on write-off of accounts receivable</t>
+          <t>Gain on loan forgiveness (Note 17)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -7047,7 +6845,7 @@
         </is>
       </c>
       <c r="F103" s="5" t="n">
-        <v>-0.000125</v>
+        <v>-0.754383</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -7063,17 +6861,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Loss on sale of marketable securities 4</t>
+          <t>Gain on write-off of deferred revenues (Note 25)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -7083,7 +6881,7 @@
         </is>
       </c>
       <c r="F104" s="5" t="n">
-        <v>-0.081</v>
+        <v>-0.297001</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -7099,27 +6897,27 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Recovery of loan receivable 7</t>
+          <t>Government grants</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F105" s="5" t="n">
-        <v>0.225</v>
+      <c r="E105" s="5" t="n">
+        <v>-0.023746</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -7135,27 +6933,27 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Write-off of prepaid expenses</t>
+          <t>Fair value change on movement in investments (Note 13)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F106" s="5" t="n">
-        <v>-0.000121</v>
+      <c r="E106" s="5" t="n">
+        <v>-0.01679</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -7171,27 +6969,25 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Write-off of deferred revenues 15</t>
+          <t>Loss on sale of marketable securities (Note 9)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E107" s="5" t="n">
+        <v>0.001528</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>0.297001</v>
+        <v>0.081</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -7207,27 +7003,27 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Write-off of assets</t>
+          <t>Provision on loan receivable (Note 5)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F108" s="5" t="n">
-        <v>-0.000652</v>
+      <c r="E108" s="5" t="n">
+        <v>18.088318</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -7243,28 +7039,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Net income (loss) for the year for continuing operations</t>
+          <t>Impairment of property and equipment, goodwill and intangible assets (Notes 7 and 8)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" s="5" t="n">
-        <v>-20.367458</v>
-      </c>
-      <c r="F109" s="5" t="n">
-        <v>14.60315</v>
-      </c>
-      <c r="G109" s="5" t="n">
-        <v>-0.583101</v>
+        <v>0.802261</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -7275,30 +7075,30 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Net income for the year for discontinued operations 1, 5, 16</t>
+          <t>Unrealized loss on marketable securities (Note 9)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E110" s="5" t="n">
+        <v>0.664813</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>3.206402</v>
-      </c>
-      <c r="G110" s="5" t="n">
-        <v>0.006837</v>
+        <v>0.49955</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -7309,34 +7109,30 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Net income (loss) for the year</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Shares issued for interest expense (Note 18)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" s="5" t="n">
+        <v>0.034619</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>17.809552</v>
-      </c>
-      <c r="G111" s="5" t="n">
-        <v>-0.576264</v>
+        <v>0.059066</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -7347,27 +7143,29 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Other Comprehensive Income</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Foreign exchange gain on translating foreign operations</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share-based payments – RSU (Note 18)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="n">
+        <v>0.088852</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>-0.03827</v>
+        <v>0.041096</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -7383,32 +7181,30 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Other Comprehensive Income</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Net and comprehensive income (loss) for the year $</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Foreign exchange loss (gain)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" s="5" t="n">
-        <v>-41.969746</v>
+        <v>-0.0063</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>17.771282</v>
-      </c>
-      <c r="G113" s="5" t="n">
-        <v>-0.576264</v>
+        <v>-0.012461</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -7419,30 +7215,32 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Net income (loss) attributable to</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Shareholders of Digicann Ventures Inc. $</t>
+          <t>Write-off of investments (Note 10)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F114" s="5" t="n">
-        <v>17.768798</v>
-      </c>
-      <c r="G114" s="5" t="n">
-        <v>-0.576264</v>
+      <c r="E114" s="5" t="n">
+        <v>1.2886</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -7453,31 +7251,29 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Net income (loss) attributable to</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Non-controlling interests 6</t>
+          <t>Write-off of accounts payable (Note 14)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>MinorityInterests</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>-0.2474</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>-0.040754</v>
+        <v>-0.679417</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -7493,30 +7289,34 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Net and comprehensive income (loss) attributable to</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Shareholders of Digicann Ventures Inc. $</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Write-off of amounts receivable (Note 4)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>0.225699</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>17.730528</v>
-      </c>
-      <c r="G116" s="5" t="n">
-        <v>-0.576264</v>
+        <v>0.000125</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -7527,31 +7327,27 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Net and comprehensive income (loss) attributable to</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Non-controlling interests 6</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>MinorityInterests</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F117" s="5" t="n">
-        <v>-0.040754</v>
+          <t>Write-off of inventory</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" s="5" t="n">
+        <v>0.01816</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -7567,30 +7363,34 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Net and comprehensive income (loss) attributable to</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Net income (loss) per share for continuing operations – basic $</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Write-off of prepaid expenses (Note 6)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>0.02535</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>1.07e-06</v>
-      </c>
-      <c r="G118" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.000121</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -7601,30 +7401,30 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Net and comprehensive income (loss) attributable to</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Net income (loss) per share for discontinued operations – basic $</t>
+          <t>Loss (gain) for the year from discontinued operations (Notes 1, 11, and 26)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E119" s="5" t="n">
+        <v>21.567279</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>2.3e-07</v>
-      </c>
-      <c r="G119" s="5" t="n">
-        <v>0</v>
+        <v>-3.206402</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -7635,34 +7435,30 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Net and comprehensive income (loss) attributable to</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Net income (loss) per share – basic $</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash used in operating activities from continued operations</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" s="5" t="n">
+        <v>-1.490595</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>1.3e-06</v>
-      </c>
-      <c r="G120" s="5" t="n">
-        <v>-3e-08</v>
+        <v>-2.747771</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -7673,17 +7469,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Net and comprehensive income (loss) attributable to</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Net income (loss) per share for continuing operations – diluted $</t>
+          <t>Proceeds from the sale of investments (Note 13)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -7693,10 +7489,12 @@
         </is>
       </c>
       <c r="F121" s="5" t="n">
-        <v>1.06e-06</v>
-      </c>
-      <c r="G121" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.225</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -7707,17 +7505,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Net and comprehensive income (loss) attributable to</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Net income (loss) per share for discontinued operations – diluted $</t>
+          <t>Proceeds from the sale of AgraFlora Europe (Note 26)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -7727,10 +7525,12 @@
         </is>
       </c>
       <c r="F122" s="5" t="n">
-        <v>2.3e-07</v>
-      </c>
-      <c r="G122" s="5" t="n">
-        <v>0</v>
+        <v>0.60822</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -7741,34 +7541,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Net and comprehensive income (loss) attributable to</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Net income (loss) per share – diluted $</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F123" s="5" t="n">
-        <v>1.29e-06</v>
-      </c>
-      <c r="G123" s="5" t="n">
-        <v>-3e-08</v>
+          <t>Investment in Twenty One (Note 10)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" s="5" t="n">
+        <v>-1.27181</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -7779,34 +7577,34 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Net and comprehensive income (loss) attributable to</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Net cash flows provided by (used in) investing activities</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="n">
+        <v>-1.263498</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>13.679729</v>
-      </c>
-      <c r="G124" s="5" t="n">
-        <v>21.12015</v>
+        <v>3.182258</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -7817,22 +7615,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Effect of change in foreign currency on cash</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" s="5" t="n">
-        <v>0.000199</v>
+        <v>-0.035009</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -7856,38 +7654,28 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cost of goods sold</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
-      <c r="E126" s="5" t="n">
-        <v>-0.00018</v>
+          <t>December 31, 2025 December</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G126" s="5" t="n">
+        <v>0.002024</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="127">
@@ -7898,32 +7686,30 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sales total</t>
+          <t>Consulting and management 10</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
-      <c r="E127" s="5" t="n">
-        <v>1.9e-05</v>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G127" s="5" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="H127" s="5" t="n">
+        <v>0.30059</v>
       </c>
     </row>
     <row r="128">
@@ -7939,31 +7725,21 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Amortization 7,8</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Corporate development</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" s="5" t="n">
-        <v>0.145242</v>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.042849</v>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>0.03792</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>0.010683</v>
+      </c>
+      <c r="H128" s="5" t="n">
+        <v>0.004811</v>
       </c>
     </row>
     <row r="129">
@@ -7979,25 +7755,25 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Consulting and management 19</t>
+          <t>Finance and other costs 7</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
-      <c r="E129" s="5" t="n">
-        <v>0.631394</v>
-      </c>
-      <c r="F129" s="5" t="n">
-        <v>0.491472</v>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>0.254921</v>
+      </c>
+      <c r="H129" s="5" t="n">
+        <v>0.263551</v>
       </c>
     </row>
     <row r="130">
@@ -8013,25 +7789,25 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Finance and other costs 16, 17</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E130" s="5" t="n">
-        <v>3.339578</v>
+        <v>0.051064</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>2.278833</v>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.126367</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>0.018205</v>
+      </c>
+      <c r="H130" s="5" t="n">
+        <v>0.057312</v>
       </c>
     </row>
     <row r="131">
@@ -8047,29 +7823,23 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Foreign exchange loss(gain)</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E131" s="5" t="n">
-        <v>-0.0063</v>
+          <t>Investor communication</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F131" s="5" t="n">
-        <v>-0.012461</v>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000514</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>0.00363</v>
+      </c>
+      <c r="H131" s="5" t="n">
+        <v>0.003894</v>
       </c>
     </row>
     <row r="132">
@@ -8085,27 +7855,21 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Development and compliance</t>
+          <t>Office and sundry</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" s="5" t="n">
-        <v>0.001413</v>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.028025</v>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>0.06821000000000001</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>0.009617000000000001</v>
+      </c>
+      <c r="H132" s="5" t="n">
+        <v>0.002882</v>
       </c>
     </row>
     <row r="133">
@@ -8121,27 +7885,25 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Due diligence</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E133" s="5" t="n">
-        <v>0.003424</v>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.635392</v>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>0.382852</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>0.165034</v>
+      </c>
+      <c r="H133" s="5" t="n">
+        <v>0.08397499999999999</v>
       </c>
     </row>
     <row r="134">
@@ -8157,27 +7919,25 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Other general and operating costs</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>Regulatory and transfer agent fees</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E134" s="5" t="n">
-        <v>0.003545</v>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.176834</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>0.152018</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>0.07457</v>
+      </c>
+      <c r="H134" s="5" t="n">
+        <v>0.077543</v>
       </c>
     </row>
     <row r="135">
@@ -8193,22 +7953,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Rent expense</t>
+          <t>Share-based payments</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
-      <c r="E135" s="5" t="n">
-        <v>0.062</v>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G135" s="5" t="n">
+        <v>0.033937</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -8229,25 +7989,25 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Share-based payment expense 18, 19</t>
+          <t>Wages and salaries (recoveries)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
-      <c r="E136" s="5" t="n">
-        <v>0.088852</v>
-      </c>
-      <c r="F136" s="5" t="n">
-        <v>0.041096</v>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>-0.009686</v>
+      </c>
+      <c r="H136" s="5" t="n">
+        <v>0.003503</v>
       </c>
     </row>
     <row r="137">
@@ -8263,25 +8023,25 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Wages and salary</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
+          <t>Loss before other items</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E137" s="5" t="n">
-        <v>0.118699</v>
+        <v>-5.321992</v>
       </c>
       <c r="F137" s="5" t="n">
-        <v>0.004834</v>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.571655</v>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>-0.895151</v>
+      </c>
+      <c r="H137" s="5" t="n">
+        <v>-0.798061</v>
       </c>
     </row>
     <row r="138">
@@ -8297,27 +8057,25 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Fair value movement oninvestments 10</t>
+          <t>Gain on debt settlement 7, 9</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
-      <c r="E138" s="5" t="n">
-        <v>0.01679</v>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G138" s="5" t="n">
+        <v>0.075054</v>
+      </c>
+      <c r="H138" s="5" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="139">
@@ -8333,25 +8091,27 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Gain on debt settlement 14,16,18</t>
+          <t>Gain on loan forgiveness 8</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
-      <c r="E139" s="5" t="n">
-        <v>3.381551</v>
-      </c>
-      <c r="F139" s="5" t="n">
-        <v>16.157433</v>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H139" s="5" t="n">
+        <v>0.075</v>
       </c>
     </row>
     <row r="140">
@@ -8367,25 +8127,25 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Gain on modification of debt 16</t>
+          <t>Gain on modification of debt 7</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
-      <c r="E140" s="5" t="n">
-        <v>1.529911</v>
-      </c>
-      <c r="F140" s="5" t="n">
-        <v>0.643019</v>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>0.163514</v>
+      </c>
+      <c r="H140" s="5" t="n">
+        <v>0.163924</v>
       </c>
     </row>
     <row r="141">
@@ -8401,25 +8161,27 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Loss on sale of marketable securities 9</t>
+          <t>Gain on termination of proposed transaction 8</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
-      <c r="E141" s="5" t="n">
-        <v>-0.001528</v>
-      </c>
-      <c r="F141" s="5" t="n">
-        <v>-0.081</v>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H141" s="5" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="142">
@@ -8435,7 +8197,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Gain on loan forgiveness 17</t>
+          <t>Unrealized loss on marketable securities 4</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -8445,12 +8207,10 @@
         </is>
       </c>
       <c r="F142" s="5" t="n">
-        <v>0.754383</v>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.49955</v>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>-0.00045</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -8471,25 +8231,25 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Gain on write-off ofaccounts payable 14</t>
+          <t>Derecognition of accounts payable 6</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
-      <c r="E143" s="5" t="n">
-        <v>0.2474</v>
-      </c>
-      <c r="F143" s="5" t="n">
-        <v>0.679417</v>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>0.073932</v>
+      </c>
+      <c r="H143" s="5" t="n">
+        <v>0.000599</v>
       </c>
     </row>
     <row r="144">
@@ -8505,7 +8265,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Sale of investments 13</t>
+          <t>Total other items</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -8514,18 +8274,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F144" s="5" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>0.31205</v>
+      </c>
+      <c r="H144" s="5" t="n">
+        <v>0.369523</v>
       </c>
     </row>
     <row r="145">
@@ -8536,32 +8294,30 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Net and comprehensive loss for the year for</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Provision on loan receivable 5</t>
+          <t>Net and comprehensive loss for the year for continuing operations</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
-      <c r="E145" s="5" t="n">
-        <v>-18.088318</v>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G145" s="5" t="n">
+        <v>-0.583101</v>
+      </c>
+      <c r="H145" s="5" t="n">
+        <v>-0.428538</v>
       </c>
     </row>
     <row r="146">
@@ -8572,27 +8328,27 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Net and comprehensive loss for the year for</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Impairment ofproperty and equipment, goodwill andintangible assets 8</t>
+          <t>Net income for the year for discontinued operations 14</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
-      <c r="E146" s="5" t="n">
-        <v>-0.802261</v>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G146" s="5" t="n">
+        <v>0.006837</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -8608,30 +8364,34 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Net and comprehensive loss for the year for</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Unrealized loss on marketable securities 9</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" s="5" t="n">
-        <v>-0.664813</v>
-      </c>
-      <c r="F147" s="5" t="n">
-        <v>-0.49955</v>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net income (loss) for the year</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G147" s="5" t="n">
+        <v>-0.576264</v>
+      </c>
+      <c r="H147" s="5" t="n">
+        <v>-0.428538</v>
       </c>
     </row>
     <row r="148">
@@ -8642,32 +8402,30 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Net income (loss) attributable to</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Government grants 17</t>
+          <t>Shareholders of Digicann Ventures Inc.</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
-      <c r="E148" s="5" t="n">
-        <v>0.023746</v>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G148" s="5" t="n">
+        <v>-0.576264</v>
+      </c>
+      <c r="H148" s="5" t="n">
+        <v>-0.428538</v>
       </c>
     </row>
     <row r="149">
@@ -8678,21 +8436,23 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Net income (loss) attributable to</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Interest income 5</t>
+          <t>Non-controlling interests</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
-        </is>
-      </c>
-      <c r="E149" s="5" t="n">
-        <v>0.657651</v>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -8718,32 +8478,26 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Net income (loss) attributable to</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Royalty revenues 21</t>
+          <t>Net income (loss) attributable to total</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" s="5" t="n">
-        <v>0.0526</v>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-41.934737</v>
+      </c>
+      <c r="F150" s="5" t="n">
+        <v>17.809552</v>
+      </c>
+      <c r="G150" s="5" t="n">
+        <v>-0.576264</v>
+      </c>
+      <c r="H150" s="5" t="n">
+        <v>-0.428538</v>
       </c>
     </row>
     <row r="151">
@@ -8754,32 +8508,30 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Net and comprehensive income (loss) attributable to</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Gain ontermination of lease 15</t>
+          <t>Shareholders of Digicann Ventures Inc.</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
-      <c r="E151" s="5" t="n">
-        <v>0.159614</v>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G151" s="5" t="n">
+        <v>-0.576264</v>
+      </c>
+      <c r="H151" s="5" t="n">
+        <v>-0.428538</v>
       </c>
     </row>
     <row r="152">
@@ -8790,22 +8542,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Net and comprehensive income (loss) attributable to</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Write-off of deferred revenues 25</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>Non-controlling interests</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F152" s="5" t="n">
-        <v>0.297001</v>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -8826,32 +8584,26 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Net and comprehensive income (loss) attributable to</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Write-off ofinvestments 10</t>
+          <t>Net and comprehensive income (loss) attributable to total</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" s="5" t="n">
-        <v>-1.2886</v>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-41.969746</v>
+      </c>
+      <c r="F153" s="5" t="n">
+        <v>17.771282</v>
+      </c>
+      <c r="G153" s="5" t="n">
+        <v>-0.576264</v>
+      </c>
+      <c r="H153" s="5" t="n">
+        <v>-0.428538</v>
       </c>
     </row>
     <row r="154">
@@ -8862,30 +8614,30 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Net and comprehensive income (loss) attributable to</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Write-off of accounts receivable 4</t>
+          <t>Net income (loss) per share for continuing operations - basic $</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
-      <c r="E154" s="5" t="n">
-        <v>-0.225699</v>
-      </c>
-      <c r="F154" s="5" t="n">
-        <v>-0.000125</v>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G154" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="H154" s="5" t="n">
+        <v>-2e-08</v>
       </c>
     </row>
     <row r="155">
@@ -8896,30 +8648,30 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Net income (loss) per share for discontinued operations</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Write-off of prepaid expenses 6</t>
+          <t>- basic $</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
-      <c r="E155" s="5" t="n">
-        <v>-0.02535</v>
-      </c>
-      <c r="F155" s="5" t="n">
-        <v>-0.000121</v>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G155" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -8930,32 +8682,34 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Net income (loss) per share for discontinued operations</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Write-off of inventory 20</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" s="5" t="n">
-        <v>-0.01816</v>
+          <t>Net income (loss) per share - basic $</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G156" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="H156" s="5" t="n">
+        <v>-2e-08</v>
       </c>
     </row>
     <row r="157">
@@ -8966,30 +8720,30 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Net income (loss) per share for discontinued operations</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Net income (loss) for the year for discontinued operations 1, 11,26</t>
+          <t>Net income (loss) per share for continuing operations - diluted $</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
-      <c r="E157" s="5" t="n">
-        <v>-21.567279</v>
-      </c>
-      <c r="F157" s="5" t="n">
-        <v>3.206402</v>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G157" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="H157" s="5" t="n">
+        <v>-2e-08</v>
       </c>
     </row>
     <row r="158">
@@ -9000,30 +8754,30 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Net income (loss) per share for discontinued operations</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Net income (loss) for the year before other items</t>
+          <t>- diluted $</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
-      <c r="E158" s="5" t="n">
-        <v>-41.934737</v>
-      </c>
-      <c r="F158" s="5" t="n">
-        <v>17.809552</v>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G158" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -9034,30 +8788,34 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Other Comprehensive Income</t>
+          <t>Net income (loss) per share for discontinued operations</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Foreign Exchange gain on translating foreignoperations</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" s="5" t="n">
-        <v>-0.035009</v>
-      </c>
-      <c r="F159" s="5" t="n">
-        <v>-0.03827</v>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net income (loss) per share - diluted $</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G159" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="H159" s="5" t="n">
+        <v>-2e-08</v>
       </c>
     </row>
     <row r="160">
@@ -9068,30 +8826,34 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Net income (loss) attributable to</t>
+          <t>Net income (loss) per share for discontinued operations</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Net income (loss) attributable to:</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
-      <c r="E160" s="5" t="n">
-        <v>-41.934737</v>
-      </c>
-      <c r="F160" s="5" t="n">
-        <v>17.768798</v>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G160" s="5" t="n">
+        <v>21.12015</v>
+      </c>
+      <c r="H160" s="5" t="n">
+        <v>22.844335</v>
       </c>
     </row>
     <row r="161">
@@ -9102,36 +8864,30 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Shareholders ofDigicann Ventures Inc.</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Non-controlling interests 12</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>MinorityInterests</t>
-        </is>
-      </c>
+          <t>Balance, December 31, 2023 17,856,672 204,391,087 4,545,209 7,993,945 (129,897) (6,153)</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F161" s="5" t="n">
-        <v>-0.040754</v>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="n">
+        <v>-0.62036</v>
+      </c>
+      <c r="H161" s="5" t="n">
+        <v>-217.414551</v>
       </c>
     </row>
     <row r="162">
@@ -9142,30 +8898,32 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Shareholders ofDigicann Ventures Inc.</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Shareholders ofDigicann Ventures Inc. total</t>
+          <t>Fair value of options expired (Note 9) - - (1,906,814) - - -</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
-      <c r="E162" s="5" t="n">
-        <v>-41.934737</v>
-      </c>
-      <c r="F162" s="5" t="n">
-        <v>17.809552</v>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H162" s="5" t="n">
+        <v>1.906814</v>
       </c>
     </row>
     <row r="163">
@@ -9176,25 +8934,27 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Net and comprehensive income (loss) attributable to</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Net and comprehensive income (loss) attributable to:</t>
+          <t>Share-based payments - Restricted Share Units (Note 9) - - 33,937 - - -</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
-      <c r="E163" s="5" t="n">
-        <v>-41.969746</v>
-      </c>
-      <c r="F163" s="5" t="n">
-        <v>17.730528</v>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="n">
+        <v>0.033937</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -9210,20 +8970,24 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Shareholders ofDigicann Ventures Inc.</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Net income (loss) per share for continuing operations – basic $</t>
+          <t>Shares issued for conversion of Restricted Share Units (Note 9) 1,696,815 33,937 (33,937) - - -</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
-      <c r="E164" s="5" t="n">
-        <v>-9.58e-06</v>
-      </c>
-      <c r="F164" s="5" t="n">
-        <v>1.07e-06</v>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -9244,25 +9008,27 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Shareholders ofDigicann Ventures Inc.</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Net income (loss) per share for discontinued operations – basic $</t>
+          <t>Shares issued for debt settlement (Note 9) 2,501,807 50,036 - - - -</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
-      <c r="E165" s="5" t="n">
-        <v>-1.015e-05</v>
-      </c>
-      <c r="F165" s="5" t="n">
-        <v>2.3e-07</v>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G165" s="5" t="n">
+        <v>0.050036</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -9278,34 +9044,34 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Shareholders ofDigicann Ventures Inc.</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Net income (loss) per share – basic $</t>
+          <t>Net loss and comprehensive loss for the year - - - - - -</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E166" s="5" t="n">
-        <v>-1.973e-05</v>
-      </c>
-      <c r="F166" s="5" t="n">
-        <v>1.3e-06</v>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G166" s="5" t="n">
+        <v>-0.576264</v>
+      </c>
+      <c r="H166" s="5" t="n">
+        <v>-0.576264</v>
       </c>
     </row>
     <row r="167">
@@ -9316,30 +9082,30 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Shareholders ofDigicann Ventures Inc.</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Net income (loss) per share for continuing operations – diluted $</t>
+          <t>Balance, December 31, 2024 22,055,294 204,475,060 2,638,395 7,993,945 (129,897) (6,153)</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
-      <c r="E167" s="5" t="n">
-        <v>-9.07e-06</v>
-      </c>
-      <c r="F167" s="5" t="n">
-        <v>1.06e-06</v>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G167" s="5" t="n">
+        <v>-1.112651</v>
+      </c>
+      <c r="H167" s="5" t="n">
+        <v>-216.084001</v>
       </c>
     </row>
     <row r="168">
@@ -9350,25 +9116,27 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Shareholders ofDigicann Ventures Inc.</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Net income (loss) per share for discontinued operations – diluted $</t>
+          <t>Shares issued for debt settlement (Note 9) 1,000,000 20,000 - - - -</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
-      <c r="E168" s="5" t="n">
-        <v>-9.6e-06</v>
-      </c>
-      <c r="F168" s="5" t="n">
-        <v>2.3e-07</v>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G168" s="5" t="n">
+        <v>0.02</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -9384,34 +9152,32 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Shareholders ofDigicann Ventures Inc.</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Net income (loss) per share – diluted $</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
-      <c r="E169" s="5" t="n">
-        <v>-1.867e-05</v>
-      </c>
-      <c r="F169" s="5" t="n">
-        <v>1.29e-06</v>
+          <t>Fair value of options expired (Note 9) - - (2,616,181) - - -</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H169" s="5" t="n">
+        <v>2.616181</v>
       </c>
     </row>
     <row r="170">
@@ -9422,31 +9188,2475 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Shareholders ofDigicann Ventures Inc.</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
+          <t>Fair value of warrants expired (Note 9) - - - (7,993,945) - -</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H170" s="5" t="n">
+        <v>7.993945</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2025 23,055,294 204,495,060 22,214 - (129,897) (6,153)</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G171" s="5" t="n">
+        <v>-1.521189</v>
+      </c>
+      <c r="H171" s="5" t="n">
+        <v>-205.902413</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Consulting and management 12</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F172" s="5" t="n">
+        <v>0.491472</v>
+      </c>
+      <c r="G172" s="5" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Finance and other costs 9, 10</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F173" s="5" t="n">
+        <v>2.278833</v>
+      </c>
+      <c r="G173" s="5" t="n">
+        <v>0.254921</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss (gain)</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E174" s="5" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="F174" s="5" t="n">
+        <v>-0.012461</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Share-based payments 11</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F175" s="5" t="n">
+        <v>0.041096</v>
+      </c>
+      <c r="G175" s="5" t="n">
+        <v>0.033937</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Wages and salary recoveries</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F176" s="5" t="n">
+        <v>0.004834</v>
+      </c>
+      <c r="G176" s="5" t="n">
+        <v>-0.009686</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="n">
+        <v>5.322011</v>
+      </c>
+      <c r="F177" s="5" t="n">
+        <v>3.571655</v>
+      </c>
+      <c r="G177" s="5" t="n">
+        <v>0.895151</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Gain on debt settlement 9,11</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F178" s="5" t="n">
+        <v>16.157433</v>
+      </c>
+      <c r="G178" s="5" t="n">
+        <v>0.075054</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Gain on loan forgiveness 10</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F179" s="5" t="n">
+        <v>0.754383</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Gain on modification of debt 9</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F180" s="5" t="n">
+        <v>0.643019</v>
+      </c>
+      <c r="G180" s="5" t="n">
+        <v>0.163514</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Derecognition of accounts payable 8</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F181" s="5" t="n">
+        <v>0.679417</v>
+      </c>
+      <c r="G181" s="5" t="n">
+        <v>0.073932</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Gain on write-off of accounts receivable</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F182" s="5" t="n">
+        <v>-0.000125</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Loss on sale of marketable securities 4</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F183" s="5" t="n">
+        <v>-0.081</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Recovery of loan receivable 7</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F184" s="5" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Write-off of prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F185" s="5" t="n">
+        <v>-0.000121</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Write-off of deferred revenues 15</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F186" s="5" t="n">
+        <v>0.297001</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Write-off of assets</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F187" s="5" t="n">
+        <v>-0.000652</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Net income (loss) for the year for continuing operations</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" s="5" t="n">
+        <v>-20.367458</v>
+      </c>
+      <c r="F188" s="5" t="n">
+        <v>14.60315</v>
+      </c>
+      <c r="G188" s="5" t="n">
+        <v>-0.583101</v>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Net income for the year for discontinued operations 1, 5, 16</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F189" s="5" t="n">
+        <v>3.206402</v>
+      </c>
+      <c r="G189" s="5" t="n">
+        <v>0.006837</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Net income (loss) for the year</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F190" s="5" t="n">
+        <v>17.809552</v>
+      </c>
+      <c r="G190" s="5" t="n">
+        <v>-0.576264</v>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Other Comprehensive Income</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Foreign exchange gain on translating foreign operations</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F191" s="5" t="n">
+        <v>-0.03827</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Other Comprehensive Income</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Net and comprehensive income (loss) for the year $</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E192" s="5" t="n">
+        <v>-41.969746</v>
+      </c>
+      <c r="F192" s="5" t="n">
+        <v>17.771282</v>
+      </c>
+      <c r="G192" s="5" t="n">
+        <v>-0.576264</v>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Net income (loss) attributable to</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Shareholders of Digicann Ventures Inc. $</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F193" s="5" t="n">
+        <v>17.768798</v>
+      </c>
+      <c r="G193" s="5" t="n">
+        <v>-0.576264</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Net income (loss) attributable to</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Non-controlling interests 6</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F194" s="5" t="n">
+        <v>-0.040754</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Net and comprehensive income (loss) attributable to</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Shareholders of Digicann Ventures Inc. $</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F195" s="5" t="n">
+        <v>17.730528</v>
+      </c>
+      <c r="G195" s="5" t="n">
+        <v>-0.576264</v>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Net and comprehensive income (loss) attributable to</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Non-controlling interests 6</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F196" s="5" t="n">
+        <v>-0.040754</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Net and comprehensive income (loss) attributable to</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Net income (loss) per share for continuing operations – basic $</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" s="5" t="n">
+        <v>-9.58e-06</v>
+      </c>
+      <c r="F197" s="5" t="n">
+        <v>1.07e-06</v>
+      </c>
+      <c r="G197" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Net and comprehensive income (loss) attributable to</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Net income (loss) per share for discontinued operations – basic $</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" s="5" t="n">
+        <v>-1.015e-05</v>
+      </c>
+      <c r="F198" s="5" t="n">
+        <v>2.3e-07</v>
+      </c>
+      <c r="G198" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Net and comprehensive income (loss) attributable to</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Net income (loss) per share – basic $</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E199" s="5" t="n">
+        <v>-1.973e-05</v>
+      </c>
+      <c r="F199" s="5" t="n">
+        <v>1.3e-06</v>
+      </c>
+      <c r="G199" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Net and comprehensive income (loss) attributable to</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Net income (loss) per share for continuing operations – diluted $</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" s="5" t="n">
+        <v>-9.07e-06</v>
+      </c>
+      <c r="F200" s="5" t="n">
+        <v>1.06e-06</v>
+      </c>
+      <c r="G200" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Net and comprehensive income (loss) attributable to</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Net income (loss) per share for discontinued operations – diluted $</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" s="5" t="n">
+        <v>-9.6e-06</v>
+      </c>
+      <c r="F201" s="5" t="n">
+        <v>2.3e-07</v>
+      </c>
+      <c r="G201" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Net and comprehensive income (loss) attributable to</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Net income (loss) per share – diluted $</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
+      <c r="E202" s="5" t="n">
+        <v>-1.867e-05</v>
+      </c>
+      <c r="F202" s="5" t="n">
+        <v>1.29e-06</v>
+      </c>
+      <c r="G202" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Net and comprehensive income (loss) attributable to</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
           <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr">
+      <c r="D203" t="inlineStr">
         <is>
           <t>SharesOutstanding</t>
         </is>
       </c>
-      <c r="E170" s="5" t="n">
+      <c r="E203" s="5" t="n">
         <v>2.126982</v>
       </c>
-      <c r="F170" s="5" t="n">
+      <c r="F203" s="5" t="n">
         <v>13.679729</v>
       </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
+      <c r="G203" s="5" t="n">
+        <v>21.12015</v>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" s="5" t="n">
+        <v>0.000199</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Cost of goods sold</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
+      <c r="E205" s="5" t="n">
+        <v>0.00018</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Sales total</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" s="5" t="n">
+        <v>1.9e-05</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Amortization 7,8</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="n">
+        <v>0.145242</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Consulting and management 19</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" s="5" t="n">
+        <v>0.631394</v>
+      </c>
+      <c r="F208" s="5" t="n">
+        <v>0.491472</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Finance and other costs 16, 17</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" s="5" t="n">
+        <v>3.339578</v>
+      </c>
+      <c r="F209" s="5" t="n">
+        <v>2.278833</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Development and compliance</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" s="5" t="n">
+        <v>0.001413</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Due diligence</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" s="5" t="n">
+        <v>0.003424</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Other general and operating costs</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" s="5" t="n">
+        <v>0.003545</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Rent expense</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" s="5" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Share-based payment expense 18, 19</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" s="5" t="n">
+        <v>0.088852</v>
+      </c>
+      <c r="F214" s="5" t="n">
+        <v>0.041096</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Wages and salary</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" s="5" t="n">
+        <v>0.118699</v>
+      </c>
+      <c r="F215" s="5" t="n">
+        <v>0.004834</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Fair value movement on investments 10</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" s="5" t="n">
+        <v>0.01679</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Gain on debt settlement 14,16,18</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" s="5" t="n">
+        <v>3.381551</v>
+      </c>
+      <c r="F217" s="5" t="n">
+        <v>16.157433</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Gain on modification of debt 16</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" s="5" t="n">
+        <v>1.529911</v>
+      </c>
+      <c r="F218" s="5" t="n">
+        <v>0.643019</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Loss on sale of marketable securities 9</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" s="5" t="n">
+        <v>-0.001528</v>
+      </c>
+      <c r="F219" s="5" t="n">
+        <v>-0.081</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Gain on loan forgiveness 17</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F220" s="5" t="n">
+        <v>0.754383</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Gain on write-off of accounts payable 14</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" s="5" t="n">
+        <v>0.2474</v>
+      </c>
+      <c r="F221" s="5" t="n">
+        <v>0.679417</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Sale of investments 13</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F222" s="5" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Provision on loan receivable 5</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" s="5" t="n">
+        <v>-18.088318</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Impairment of property and equipment, goodwill and intangible assets 8</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" s="5" t="n">
+        <v>-0.802261</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Unrealized loss on marketable securities 9</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" s="5" t="n">
+        <v>-0.664813</v>
+      </c>
+      <c r="F225" s="5" t="n">
+        <v>-0.49955</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Government grants 17</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" s="5" t="n">
+        <v>0.023746</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Interest income 5</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
+      <c r="E227" s="5" t="n">
+        <v>0.657651</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Royalty revenues 21</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" s="5" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Gain on termination of lease 15</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" s="5" t="n">
+        <v>0.159614</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Write-off of deferred revenues 25</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F230" s="5" t="n">
+        <v>0.297001</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Write-off of investments 10</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" s="5" t="n">
+        <v>-1.2886</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Write-off of accounts receivable 4</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" s="5" t="n">
+        <v>-0.225699</v>
+      </c>
+      <c r="F232" s="5" t="n">
+        <v>-0.000125</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Write-off of prepaid expenses 6</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" s="5" t="n">
+        <v>-0.02535</v>
+      </c>
+      <c r="F233" s="5" t="n">
+        <v>-0.000121</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Write-off of inventory 20</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" s="5" t="n">
+        <v>-0.01816</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Net income (loss) for the year for discontinued operations 1, 11, 26</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" s="5" t="n">
+        <v>-21.567279</v>
+      </c>
+      <c r="F235" s="5" t="n">
+        <v>3.206402</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Net income (loss) for the year before other items</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" s="5" t="n">
+        <v>-41.934737</v>
+      </c>
+      <c r="F236" s="5" t="n">
+        <v>17.809552</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Other Comprehensive Income</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Foreign Exchange gain on translating foreign operations</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" s="5" t="n">
+        <v>-0.035009</v>
+      </c>
+      <c r="F237" s="5" t="n">
+        <v>-0.03827</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Net income (loss) attributable to</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Non-controlling interests 12</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F238" s="5" t="n">
+        <v>-0.040754</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Net and comprehensive income (loss) attributable to</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Non-controlling interests 12</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F239" s="5" t="n">
+        <v>-0.040754</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/DCNN.X.xlsx
+++ b/output/pdf_financials_xlsx/DCNN.X.xlsx
@@ -2231,16 +2231,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>25.066524</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>12.539154</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>10.63234</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.022214</v>
       </c>
     </row>
     <row r="93">
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0.02535</v>
+        <v>-0.005865</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0.000121</v>
+        <v>0.057063</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>0</v>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.254049</v>
+        <v>0.222834</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-2.405775</v>
+        <v>-2.348833</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>0.157526</v>
@@ -3478,7 +3478,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -4074,7 +4078,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -4440,7 +4448,11 @@
           <t>Prepaids and deposits 6</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E37" s="5" t="n">
         <v>0.057063</v>
       </c>
@@ -4736,7 +4748,11 @@
           <t>Reserves 18</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" s="5" t="n">
         <v>25.066524</v>
       </c>
@@ -6120,7 +6136,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E83" s="5" t="n">
         <v>-0.031215</v>
       </c>

--- a/output/pdf_financials_xlsx/DCNN.X.xlsx
+++ b/output/pdf_financials_xlsx/DCNN.X.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.657651</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-41.969746</v>
+        <v>-42.627397</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>17.809552</v>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-41.969746</v>
+        <v>-42.627397</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>17.809552</v>
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.304255</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.738742</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.293907</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.183072</v>
       </c>
     </row>
     <row r="35">
@@ -1127,16 +1127,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.5753470000000001</v>
+        <v>0.879602</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.00045</v>
+        <v>0.739192</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.293907</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.183072</v>
       </c>
     </row>
     <row r="37">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E227" s="5" t="n">

--- a/output/pdf_financials_xlsx/DCNN.X.xlsx
+++ b/output/pdf_financials_xlsx/DCNN.X.xlsx
@@ -1683,16 +1683,16 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.9456909999999999</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.113483</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.082826</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.110101</v>
       </c>
     </row>
     <row r="65">
@@ -1740,16 +1740,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.095737</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="68">
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.008312</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>2.349038</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -6496,7 +6496,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E93" s="5" t="n">
         <v>0.008312</v>
       </c>
@@ -7502,7 +7506,11 @@
           <t>Proceeds from the sale of investments (Note 13)</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
